--- a/gangho/docs/상성시스템_총정리.xlsx
+++ b/gangho/docs/상성시스템_총정리.xlsx
@@ -751,7 +751,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>이기면 주는 +15% · 받는 −15%</t>
+          <t>이기면 주는 +12% · 받는 −12%</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>한 단계 차이마다 ±10%, 최대 3단계(±30%)</t>
+          <t>한 단계 차이마다 ±8%, 최대 3단계(±24%)</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -1276,8 +1276,8 @@
       <c r="C18" s="8" t="n">
         <v>0.15</v>
       </c>
-      <c r="D18" s="8" t="n">
-        <v>0.15</v>
+      <c r="D18" s="9" t="n">
+        <v>0.12</v>
       </c>
       <c r="E18" s="10">
         <f>D18-C18</f>
@@ -1303,8 +1303,8 @@
       <c r="C19" s="8" t="n">
         <v>0.1</v>
       </c>
-      <c r="D19" s="8" t="n">
-        <v>0.1</v>
+      <c r="D19" s="9" t="n">
+        <v>0.08</v>
       </c>
       <c r="E19" s="10">
         <f>D19-C19</f>

--- a/gangho/docs/상성시스템_총정리.xlsx
+++ b/gangho/docs/상성시스템_총정리.xlsx
@@ -548,7 +548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -800,44 +800,76 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
+          <t>두목 보정</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>두목 요수 (모두 대형)</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>상성으로 얻는 이득</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>주는 피해 + · 받는 피해 − · 명중 + 몫을 절반으로 (손해는 그대로)</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>martial_arts.js AFFINITY.bossGain · combat_engine.js affinity()</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>오행 · 병기 · 크기 · 약점 모두. 예: 창으로 적염 호랑이 = 크기 +30% → +15%, 병기 우세 +12% → +6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
           <t>지형</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>장착 경공의 지형 ↔ 탐험지 지형</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>강호행 기력 소모</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>맞으면 −20% · 하나도 안 맞으면 +20% · 경공 없으면 0</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>martial_arts.js AFFINITY.terrainMatch · terrainMiss · areas.js terrain</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>전투 피해와는 무관</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>계산 순서: 주는 피해 = 기본 피해 × 오행 × 병기 × (1+약점) × (1+크기) × 경지 × 정마사 · 받는 피해 = 기본 × 오행 × 병기 × 경지 × 정마사</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>출처: 게임 코드 (js/data/martial_arts.js · monsters.js · areas.js, js/systems/combat_engine.js affinity()). 크기 상성 처음 안은 유저 제안, 하향 폭은 Claude가 정함.</t>
         </is>
@@ -854,7 +886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1394,6 +1426,33 @@
       <c r="F22" s="5" t="inlineStr">
         <is>
           <t>AFFINITY.terrainMiss</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>두목</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>상성 이득 비율 (손해는 그대로)</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E23" s="10">
+        <f>D23-C23</f>
+        <v/>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>AFFINITY.bossGain</t>
         </is>
       </c>
     </row>
@@ -4991,7 +5050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5163,38 +5222,58 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
+          <t>두목 상대 주는 피해 최고 (창 · 이득 절반)</t>
+        </is>
+      </c>
+      <c r="B12" s="18">
+        <f>(1+'계수'!C5*'계수'!C23)*(1+'계수'!C7*'계수'!C23)*(1+'계수'!C12*'계수'!C23)</f>
+        <v/>
+      </c>
+      <c r="C12" s="18">
+        <f>(1+'계수'!D5*'계수'!D23)*(1+'계수'!D7*'계수'!D23)*(1+'계수'!D12*'계수'!D23)</f>
+        <v/>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>두목은 모두 대형</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
           <t>경지 3단계 위 + 주는 피해 최고</t>
         </is>
       </c>
-      <c r="B12" s="18">
+      <c r="B13" s="18">
         <f>(1+'계수'!C5)*(1+'계수'!C7)*(1+'계수'!C12)*(1+'계수'!C19*'계수'!C20)</f>
         <v/>
       </c>
-      <c r="C12" s="18">
+      <c r="C13" s="18">
         <f>(1+'계수'!D5)*(1+'계수'!D7)*(1+'계수'!D12)*(1+'계수'!D19*'계수'!D20)</f>
         <v/>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>참고</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>주는 피해 폭 (최고 ÷ 최저)</t>
         </is>
       </c>
-      <c r="B13" s="19">
+      <c r="B14" s="19">
         <f>B5/B7</f>
         <v/>
       </c>
-      <c r="C13" s="19">
+      <c r="C14" s="19">
         <f>C5/C7</f>
         <v/>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>작을수록 상성이 덜 극단적</t>
         </is>

--- a/gangho/docs/상성시스템_총정리.xlsx
+++ b/gangho/docs/상성시스템_총정리.xlsx
@@ -134,19 +134,19 @@
     <xf numFmtId="9" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -548,7 +548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -562,7 +562,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>강호견문록 상성 시스템 총정리 (10월 3일 기준)</t>
+          <t>강호견문록 상성 시스템 총정리 (10월 3일 · 보완 대책 반영)</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>목극토 · 토극수 · 수극화 · 화극금 · 금극목. 상생은 보정 없음. 오성(오행 위력)은 내가 극할 때 더 세게, 오행 내성은 극당할 때 덜 아프게</t>
+          <t>목극토 · 토극수 · 수극화 · 화극금 · 금극목. 오성(오행 위력)은 내가 극할 때 더, 오행 내성은 극당할 때 덜</t>
         </is>
       </c>
     </row>
@@ -665,7 +665,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>검 · 도는 같은 계열(검/도). 가위바위보 4계열</t>
+          <t>네 계열이 한 바퀴: 권장 › 검/도 › 창 › 암기 › 권장 (보완 대책 10월 3일)</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>유리 +15 · 불리 −15 · 창→대형 +30 · 검 불리 −8 · 권장 0</t>
+          <t>범용(암기 · 도) 유리 +10 · 불리 −15 · 창 불리 −10 · 대형 +30 · 검 소형 +15 · 중형 0 · 대형 −5</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>크기 경계의 작음 · 큼은 이웃 크기 쪽으로 1/4 기울임</t>
+          <t>병기 계열 × 크기는 합쳐서 ±30% 안 (AFFINITY_CAP.weapSize)</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>청령목괴 ← 화 +20% · 염화석괴 ← 수 +40% · 빙화수요 ← 토 +20%</t>
+          <t>청령목괴 ← 화 · 염화석괴 ← 목 +40% · 빙화수요 ← 화 +40% · 두목 셋 ← 토 · 목 · 금 +25%</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>특정 요수만</t>
+          <t>오행 고리 밖의 조합. 두목에게도 줄지 않음</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>내 성향 ↔ 상대 성향</t>
+          <t>무공 칸 성향(공격) · 심법 칸 성향(방어) ↔ 사람형 요수 성향</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -751,125 +751,157 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>이기면 주는 +12% · 받는 −12%</t>
+          <t>이기면 +12% / 지면 −12%</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>martial_arts.js SCHOOL_RULES.edge · SCHOOLS.beats</t>
+          <t>martial_arts.js SCHOOL_RULES.edge · monsters.js school</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>정 › 마 › 사 › 정. 지금 요수에게는 성향이 없어 적용되지 않음 (사람끼리 겨룰 때를 위해 둠)</t>
+          <t>흑풍채 · 낭인 = 마 · 염화채 = 사 · 수룡방 = 정. 짐승 · 요괴는 성향 없음</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>경지 압제</t>
+          <t>두목 보정</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>내 품계 ↔ 요수 경지(탐험지 단계)</t>
+          <t>두목 요수 (모두 대형)</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>주는 · 받는 피해</t>
+          <t>오행 · 병기 · 크기 · 정마사</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>한 단계 차이마다 ±8%, 최대 3단계(±24%)</t>
+          <t>이득 · 손해 모두 절반 (주는 · 받는 피해 · 명중 모두)</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>martial_arts.js COMBAT_RULES.realm</t>
+          <t>martial_arts.js AFFINITY.bossGain · combat_engine.js affinity()</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>상성이라기보다 등급 차이. 곱 범위 계산에서는 뺌</t>
+          <t>격이 달라 상성이 절반만 통함. 고유 약점 · 경지 압제는 그대로</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>두목 보정</t>
+          <t>상한</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>두목 요수 (모두 대형)</t>
+          <t>상성을 다 곱한 값</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>상성으로 얻는 이득</t>
+          <t>주는 · 받는 피해</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>주는 피해 + · 받는 피해 − · 명중 + 몫을 절반으로 (손해는 그대로)</t>
+          <t>주는 0.6~1.8배 · 받는 0.7~1.5배</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>martial_arts.js AFFINITY.bossGain · combat_engine.js affinity()</t>
+          <t>martial_arts.js AFFINITY_CAP</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>오행 · 병기 · 크기 · 약점 모두. 예: 창으로 적염 호랑이 = 크기 +30% → +15%, 병기 우세 +12% → +6%</t>
+          <t>경지 압제는 상한 밖에서 따로 곱함</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
+          <t>경지 압제</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>내 품계 ↔ 요수 경지(탐험지 단계)</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>주는 · 받는 피해</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>한 단계 차이마다 ±8%, 최대 3단계(±24%)</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>martial_arts.js COMBAT_RULES.realm</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>상성이 아니라 실력 차이 — 두목에게도 그대로</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
           <t>지형</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>장착 경공의 지형 ↔ 탐험지 지형</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>강호행 기력 소모</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>맞으면 −20% · 하나도 안 맞으면 +20% · 경공 없으면 0</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>맞으면 −20% · 안 맞아도 벌점 없음 · 경공 없으면 0</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>martial_arts.js AFFINITY.terrainMatch · terrainMiss · areas.js terrain</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>전투 피해와는 무관</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>계산 순서: 주는 피해 = 기본 피해 × 오행 × 병기 × (1+약점) × (1+크기) × 경지 × 정마사 · 받는 피해 = 기본 × 오행 × 병기 × 경지 × 정마사</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>계산 순서: 주는 피해 = 기본 × 상한[ 오행 × (병기 × 크기 ±30%) × 정마사(무공 칸) × (1+약점) ] × 경지 · 받는 피해 = 기본 × 상한[ 오행 × 병기 × 정마사(심법 칸) ] × 경지 · 두목은 [ ] 안의 오행 · 병기 · 크기 · 정마사가 절반</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>출처: 게임 코드 (js/data/martial_arts.js · monsters.js · areas.js, js/systems/combat_engine.js affinity()). 크기 상성 처음 안은 유저 제안, 하향 폭은 Claude가 정함.</t>
         </is>
@@ -886,7 +918,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -907,7 +939,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>노란 칸 = 10월 3일 하향으로 바뀐 값. 조정 전은 비교용</t>
+          <t>노란 칸 = 「상성 시스템 보완 대책」으로 바뀐 값. C열은 보완 전 (0 = 그때는 없던 규칙)</t>
         </is>
       </c>
     </row>
@@ -924,7 +956,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>조정 전</t>
+          <t>보완 전</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -934,7 +966,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>줄인 폭</t>
+          <t>바뀐 폭</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -955,12 +987,12 @@
         </is>
       </c>
       <c r="C5" s="8" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D5" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="E5" s="10">
+      <c r="D5" s="8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E5" s="9">
         <f>D5-C5</f>
         <v/>
       </c>
@@ -982,12 +1014,12 @@
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D6" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="E6" s="10">
+      <c r="D6" s="8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E6" s="9">
         <f>D6-C6</f>
         <v/>
       </c>
@@ -1009,12 +1041,12 @@
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D7" s="9" t="n">
         <v>0.12</v>
       </c>
-      <c r="E7" s="10">
+      <c r="D7" s="8" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E7" s="9">
         <f>D7-C7</f>
         <v/>
       </c>
@@ -1036,12 +1068,12 @@
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D8" s="9" t="n">
         <v>0.12</v>
       </c>
-      <c r="E8" s="10">
+      <c r="D8" s="8" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E8" s="9">
         <f>D8-C8</f>
         <v/>
       </c>
@@ -1062,13 +1094,13 @@
           <t>우세 명중 보정 (%p)</t>
         </is>
       </c>
-      <c r="C9" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="D9" s="12" t="n">
+      <c r="C9" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="E9" s="13">
+      <c r="D9" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="E9" s="11">
         <f>D9-C9</f>
         <v/>
       </c>
@@ -1086,16 +1118,16 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>유리</t>
+          <t>범용(암기 · 도) 유리</t>
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="D10" s="9" t="n">
         <v>0.15</v>
       </c>
-      <c r="E10" s="10">
+      <c r="D10" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E10" s="9">
         <f>D10-C10</f>
         <v/>
       </c>
@@ -1113,16 +1145,16 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>불리</t>
+          <t>범용(암기 · 도) 불리</t>
         </is>
       </c>
       <c r="C11" s="8" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="D11" s="9" t="n">
         <v>0.15</v>
       </c>
-      <c r="E11" s="10">
+      <c r="D11" s="8" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E11" s="9">
         <f>D11-C11</f>
         <v/>
       </c>
@@ -1144,12 +1176,12 @@
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="D12" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="E12" s="10">
+      <c r="D12" s="8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E12" s="9">
         <f>D12-C12</f>
         <v/>
       </c>
@@ -1167,16 +1199,16 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>검 불리 (덜 깎임)</t>
+          <t>검 → 대형 불리</t>
         </is>
       </c>
       <c r="C13" s="8" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D13" s="9" t="n">
         <v>0.08</v>
       </c>
-      <c r="E13" s="10">
+      <c r="D13" s="12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E13" s="9">
         <f>D13-C13</f>
         <v/>
       </c>
@@ -1203,7 +1235,7 @@
       <c r="D14" s="8" t="n">
         <v>0.25</v>
       </c>
-      <c r="E14" s="10">
+      <c r="E14" s="9">
         <f>D14-C14</f>
         <v/>
       </c>
@@ -1225,12 +1257,12 @@
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D15" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="E15" s="10">
+      <c r="D15" s="8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E15" s="9">
         <f>D15-C15</f>
         <v/>
       </c>
@@ -1248,16 +1280,16 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>염화석괴 ← 수</t>
+          <t>염화석괴 ← 목 (보완 전: 수)</t>
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D16" s="9" t="n">
         <v>0.4</v>
       </c>
-      <c r="E16" s="10">
+      <c r="D16" s="8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E16" s="9">
         <f>D16-C16</f>
         <v/>
       </c>
@@ -1275,16 +1307,16 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>빙화수요 ← 토</t>
+          <t>빙화수요 ← 화 (보완 전: 토 20%)</t>
         </is>
       </c>
       <c r="C17" s="8" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D17" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="E17" s="10">
+      <c r="D17" s="12" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E17" s="9">
         <f>D17-C17</f>
         <v/>
       </c>
@@ -1306,12 +1338,12 @@
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D18" s="9" t="n">
         <v>0.12</v>
       </c>
-      <c r="E18" s="10">
+      <c r="D18" s="8" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E18" s="9">
         <f>D18-C18</f>
         <v/>
       </c>
@@ -1333,12 +1365,12 @@
         </is>
       </c>
       <c r="C19" s="8" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D19" s="9" t="n">
         <v>0.08</v>
       </c>
-      <c r="E19" s="10">
+      <c r="D19" s="8" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E19" s="9">
         <f>D19-C19</f>
         <v/>
       </c>
@@ -1359,13 +1391,13 @@
           <t>최대 단계</t>
         </is>
       </c>
-      <c r="C20" s="11" t="n">
+      <c r="C20" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="D20" s="11" t="n">
+      <c r="D20" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="E20" s="13">
+      <c r="E20" s="11">
         <f>D20-C20</f>
         <v/>
       </c>
@@ -1392,7 +1424,7 @@
       <c r="D21" s="8" t="n">
         <v>0.8</v>
       </c>
-      <c r="E21" s="10">
+      <c r="E21" s="9">
         <f>D21-C21</f>
         <v/>
       </c>
@@ -1416,10 +1448,10 @@
       <c r="C22" s="8" t="n">
         <v>1.2</v>
       </c>
-      <c r="D22" s="8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="E22" s="10">
+      <c r="D22" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="9">
         <f>D22-C22</f>
         <v/>
       </c>
@@ -1437,22 +1469,292 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>상성 이득 비율 (손해는 그대로)</t>
+          <t>상성이 통하는 비율 (이득 · 손해 모두)</t>
         </is>
       </c>
       <c r="C23" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D23" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="E23" s="10">
+      <c r="D23" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E23" s="9">
         <f>D23-C23</f>
         <v/>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
           <t>AFFINITY.bossGain</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>크기</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>창 불리</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D24" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E24" s="9">
+        <f>D24-C24</f>
+        <v/>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>SIZE_DMG</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>크기</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>검 → 소형 유리</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D25" s="8" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E25" s="9">
+        <f>D25-C25</f>
+        <v/>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>SIZE_DMG</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>크기</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>검 → 중형 불리</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="D26" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="9">
+        <f>D26-C26</f>
+        <v/>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>SIZE_DMG</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>상한</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>병기 계열 × 크기 (±)</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E27" s="9">
+        <f>D27-C27</f>
+        <v/>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>AFFINITY_CAP.weapSize</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>상한</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>주는 피해 최저 (배)</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="13" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E28" s="11">
+        <f>D28-C28</f>
+        <v/>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>AFFINITY_CAP.dealt</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>상한</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>주는 피해 최고 (배)</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E29" s="11">
+        <f>D29-C29</f>
+        <v/>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>AFFINITY_CAP.dealt</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>상한</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>받는 피해 최저 (배)</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="13" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E30" s="11">
+        <f>D30-C30</f>
+        <v/>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>AFFINITY_CAP.taken</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>상한</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>받는 피해 최고 (배)</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E31" s="11">
+        <f>D31-C31</f>
+        <v/>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>AFFINITY_CAP.taken</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>약점</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>두목 고유 약점 (적염 호랑이 ← 토 · 적패천 ← 목 · 벽해룡 ← 금)</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E32" s="9">
+        <f>D32-C32</f>
+        <v/>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>monsters.js weak</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>예시</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>오성 오행 위력 (예: 오성 10점 = +25%)</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D33" s="8" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E33" s="9">
+        <f>D33-C33</f>
+        <v/>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>APTS.wit.per.elem × 오성</t>
         </is>
       </c>
     </row>
@@ -1922,9 +2224,8 @@
         <f>'계수'!$D$7</f>
         <v/>
       </c>
-      <c r="D6" s="15">
-        <f>-'계수'!$D$8</f>
-        <v/>
+      <c r="D6" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="E6" s="15">
         <f>-'계수'!$D$8</f>
@@ -1948,9 +2249,8 @@
         <f>'계수'!$D$7</f>
         <v/>
       </c>
-      <c r="E7" s="15">
-        <f>'계수'!$D$7</f>
-        <v/>
+      <c r="E7" s="15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1959,9 +2259,8 @@
           <t>창</t>
         </is>
       </c>
-      <c r="B8" s="15">
-        <f>'계수'!$D$7</f>
-        <v/>
+      <c r="B8" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="C8" s="15">
         <f>-'계수'!$D$8</f>
@@ -1970,8 +2269,9 @@
       <c r="D8" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="E8" s="15" t="n">
-        <v>0</v>
+      <c r="E8" s="15">
+        <f>'계수'!$D$7</f>
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -1984,12 +2284,12 @@
         <f>'계수'!$D$7</f>
         <v/>
       </c>
-      <c r="C9" s="15">
+      <c r="C9" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="15">
         <f>-'계수'!$D$8</f>
         <v/>
-      </c>
-      <c r="D9" s="15" t="n">
-        <v>0</v>
       </c>
       <c r="E9" s="15" t="n">
         <v>0</v>
@@ -2042,9 +2342,8 @@
         <f>-'계수'!$D$8</f>
         <v/>
       </c>
-      <c r="D13" s="15">
-        <f>'계수'!$D$7</f>
-        <v/>
+      <c r="D13" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="E13" s="15">
         <f>'계수'!$D$7</f>
@@ -2068,9 +2367,8 @@
         <f>-'계수'!$D$8</f>
         <v/>
       </c>
-      <c r="E14" s="15">
-        <f>-'계수'!$D$8</f>
-        <v/>
+      <c r="E14" s="15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -2079,9 +2377,8 @@
           <t>창</t>
         </is>
       </c>
-      <c r="B15" s="15">
-        <f>-'계수'!$D$8</f>
-        <v/>
+      <c r="B15" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="C15" s="15">
         <f>'계수'!$D$7</f>
@@ -2090,8 +2387,9 @@
       <c r="D15" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="E15" s="15" t="n">
-        <v>0</v>
+      <c r="E15" s="15">
+        <f>-'계수'!$D$8</f>
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -2104,12 +2402,12 @@
         <f>-'계수'!$D$8</f>
         <v/>
       </c>
-      <c r="C16" s="15">
+      <c r="C16" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="15">
         <f>'계수'!$D$7</f>
         <v/>
-      </c>
-      <c r="D16" s="15" t="n">
-        <v>0</v>
       </c>
       <c r="E16" s="15" t="n">
         <v>0</v>
@@ -2162,9 +2460,8 @@
         <f>'계수'!$D$9</f>
         <v/>
       </c>
-      <c r="D20" s="16">
-        <f>-'계수'!$D$9</f>
-        <v/>
+      <c r="D20" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="E20" s="16">
         <f>-'계수'!$D$9</f>
@@ -2188,9 +2485,8 @@
         <f>'계수'!$D$9</f>
         <v/>
       </c>
-      <c r="E21" s="16">
-        <f>'계수'!$D$9</f>
-        <v/>
+      <c r="E21" s="16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2199,9 +2495,8 @@
           <t>창</t>
         </is>
       </c>
-      <c r="B22" s="16">
-        <f>'계수'!$D$9</f>
-        <v/>
+      <c r="B22" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="C22" s="16">
         <f>-'계수'!$D$9</f>
@@ -2210,8 +2505,9 @@
       <c r="D22" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="E22" s="16" t="n">
-        <v>0</v>
+      <c r="E22" s="16">
+        <f>'계수'!$D$9</f>
+        <v/>
       </c>
     </row>
     <row r="23">
@@ -2224,12 +2520,12 @@
         <f>'계수'!$D$9</f>
         <v/>
       </c>
-      <c r="C23" s="16">
+      <c r="C23" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="16">
         <f>-'계수'!$D$9</f>
         <v/>
-      </c>
-      <c r="D23" s="16" t="n">
-        <v>0</v>
       </c>
       <c r="E23" s="16" t="n">
         <v>0</v>
@@ -2238,7 +2534,7 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>한 줄로: 권장 › 검/도 › 창 · 암기 › 권장 (창과 암기는 서로 호각, 창은 권장에 강하고 검/도에 약함)</t>
+          <t>한 바퀴: 권장 › 검/도 › 창 › 암기 › 권장 — 모든 계열이 하나를 이기고 하나에게 지며, 맞은편(권장-창 · 검/도-암기)과는 호각</t>
         </is>
       </c>
     </row>
@@ -2388,11 +2684,11 @@
         </is>
       </c>
       <c r="B7" s="17">
-        <f>-'계수'!$D$11</f>
+        <f>-'계수'!$D$24</f>
         <v/>
       </c>
       <c r="C7" s="17">
-        <f>-'계수'!$D$11</f>
+        <f>-'계수'!$D$24</f>
         <v/>
       </c>
       <c r="D7" s="17">
@@ -2412,11 +2708,11 @@
         </is>
       </c>
       <c r="B8" s="17">
-        <f>'계수'!$D$10</f>
+        <f>'계수'!$D$25</f>
         <v/>
       </c>
       <c r="C8" s="17">
-        <f>-'계수'!$D$13</f>
+        <f>-'계수'!$D$26</f>
         <v/>
       </c>
       <c r="D8" s="17">
@@ -2758,13 +3054,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2777,7 +3076,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>정마사: 내 성향(세로) × 상대 성향(가로) 주는 피해 · 지금은 요수에게 성향이 없어 쓰이지 않음</t>
+          <t>정마사: 내 성향(세로) × 상대 성향(가로) 주는 피해. 공격은 무공 칸의 성향, 방어(받는 피해)는 심법 칸의 성향으로 따로 봄</t>
         </is>
       </c>
     </row>
@@ -2802,6 +3101,21 @@
           <t>사 邪</t>
         </is>
       </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>세력 (사람형 요수)</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>성향</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>유리한 내 성향</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
@@ -2820,6 +3134,21 @@
         <f>-'계수'!$D$18</f>
         <v/>
       </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>흑풍채 (청풍산) · 떠돌이 낭인</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>마 魔</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>정 正</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
@@ -2838,6 +3167,21 @@
         <f>'계수'!$D$18</f>
         <v/>
       </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>염화채 (적패천 포함)</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>사 邪</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>마 魔</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
@@ -2855,6 +3199,38 @@
       </c>
       <c r="D7" s="15" t="n">
         <v>0</v>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>수룡방 (벽해룡 포함)</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>정 正</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>사 邪</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>짐승 · 요괴</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -2982,7 +3358,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>요수 경지 = 탐험지 단계 − 1 (청풍산 0 · 염화채 1 · 수룡방 2), 제자 품계 = 삼류 0 · 이류 1 …</t>
+          <t>요수 경지 = 탐험지 단계 − 1 (청풍산 0 · 염화채 1 · 수룡방 2), 제자 품계 = 삼류 0 · 이류 1 … · 경지 압제는 상성 상한 밖에서 따로 곱하고 두목에게도 줄지 않음</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M35"/>
+  <dimension ref="A1:N35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3191,11 +3567,12 @@
     <col width="7" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
     <col width="7" customWidth="1" min="10" max="10"/>
     <col width="7" customWidth="1" min="11" max="11"/>
     <col width="7" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="7" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3208,7 +3585,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>병기별 크기 상성은 「크기」 시트에서 가져옴 (초록 글자). 떠돌이 낭인은 기연 전투용</t>
+          <t>병기별 크기 상성은 「크기」 시트에서 가져옴 (초록 글자, 두목은 실제로 이 값의 절반). 떠돌이 낭인은 기연 전투용</t>
         </is>
       </c>
     </row>
@@ -3255,25 +3632,30 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
+          <t>성향</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>권장</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>검</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>도</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>창</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>암기(표창)</t>
         </is>
@@ -3314,23 +3696,24 @@
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr"/>
-      <c r="I5" s="17">
+      <c r="I5" s="7" t="inlineStr"/>
+      <c r="J5" s="17">
         <f>'크기'!B17</f>
         <v/>
       </c>
-      <c r="J5" s="17">
+      <c r="K5" s="17">
         <f>'크기'!B16</f>
         <v/>
       </c>
-      <c r="K5" s="17">
+      <c r="L5" s="17">
         <f>'크기'!B14</f>
         <v/>
       </c>
-      <c r="L5" s="17">
+      <c r="M5" s="17">
         <f>'크기'!B15</f>
         <v/>
       </c>
-      <c r="M5" s="17">
+      <c r="N5" s="17">
         <f>'크기'!B13</f>
         <v/>
       </c>
@@ -3370,23 +3753,24 @@
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr"/>
-      <c r="I6" s="17">
+      <c r="I6" s="7" t="inlineStr"/>
+      <c r="J6" s="17">
         <f>'크기'!D17</f>
         <v/>
       </c>
-      <c r="J6" s="17">
+      <c r="K6" s="17">
         <f>'크기'!D16</f>
         <v/>
       </c>
-      <c r="K6" s="17">
+      <c r="L6" s="17">
         <f>'크기'!D14</f>
         <v/>
       </c>
-      <c r="L6" s="17">
+      <c r="M6" s="17">
         <f>'크기'!D15</f>
         <v/>
       </c>
-      <c r="M6" s="17">
+      <c r="N6" s="17">
         <f>'크기'!D13</f>
         <v/>
       </c>
@@ -3426,23 +3810,28 @@
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr"/>
-      <c r="I7" s="17">
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>마</t>
+        </is>
+      </c>
+      <c r="J7" s="17">
         <f>'크기'!E17</f>
         <v/>
       </c>
-      <c r="J7" s="17">
+      <c r="K7" s="17">
         <f>'크기'!E16</f>
         <v/>
       </c>
-      <c r="K7" s="17">
+      <c r="L7" s="17">
         <f>'크기'!E14</f>
         <v/>
       </c>
-      <c r="L7" s="17">
+      <c r="M7" s="17">
         <f>'크기'!E15</f>
         <v/>
       </c>
-      <c r="M7" s="17">
+      <c r="N7" s="17">
         <f>'크기'!E13</f>
         <v/>
       </c>
@@ -3482,23 +3871,24 @@
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr"/>
-      <c r="I8" s="17">
+      <c r="I8" s="7" t="inlineStr"/>
+      <c r="J8" s="17">
         <f>'크기'!F17</f>
         <v/>
       </c>
-      <c r="J8" s="17">
+      <c r="K8" s="17">
         <f>'크기'!F16</f>
         <v/>
       </c>
-      <c r="K8" s="17">
+      <c r="L8" s="17">
         <f>'크기'!F14</f>
         <v/>
       </c>
-      <c r="L8" s="17">
+      <c r="M8" s="17">
         <f>'크기'!F15</f>
         <v/>
       </c>
-      <c r="M8" s="17">
+      <c r="N8" s="17">
         <f>'크기'!F13</f>
         <v/>
       </c>
@@ -3538,23 +3928,24 @@
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr"/>
-      <c r="I9" s="17">
+      <c r="I9" s="7" t="inlineStr"/>
+      <c r="J9" s="17">
         <f>'크기'!C17</f>
         <v/>
       </c>
-      <c r="J9" s="17">
+      <c r="K9" s="17">
         <f>'크기'!C16</f>
         <v/>
       </c>
-      <c r="K9" s="17">
+      <c r="L9" s="17">
         <f>'크기'!C14</f>
         <v/>
       </c>
-      <c r="L9" s="17">
+      <c r="M9" s="17">
         <f>'크기'!C15</f>
         <v/>
       </c>
-      <c r="M9" s="17">
+      <c r="N9" s="17">
         <f>'크기'!C13</f>
         <v/>
       </c>
@@ -3594,23 +3985,28 @@
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr"/>
-      <c r="I10" s="17">
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>마</t>
+        </is>
+      </c>
+      <c r="J10" s="17">
         <f>'크기'!F17</f>
         <v/>
       </c>
-      <c r="J10" s="17">
+      <c r="K10" s="17">
         <f>'크기'!F16</f>
         <v/>
       </c>
-      <c r="K10" s="17">
+      <c r="L10" s="17">
         <f>'크기'!F14</f>
         <v/>
       </c>
-      <c r="L10" s="17">
+      <c r="M10" s="17">
         <f>'크기'!F15</f>
         <v/>
       </c>
-      <c r="M10" s="17">
+      <c r="N10" s="17">
         <f>'크기'!F13</f>
         <v/>
       </c>
@@ -3650,23 +4046,28 @@
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr"/>
-      <c r="I11" s="17">
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>마</t>
+        </is>
+      </c>
+      <c r="J11" s="17">
         <f>'크기'!F17</f>
         <v/>
       </c>
-      <c r="J11" s="17">
+      <c r="K11" s="17">
         <f>'크기'!F16</f>
         <v/>
       </c>
-      <c r="K11" s="17">
+      <c r="L11" s="17">
         <f>'크기'!F14</f>
         <v/>
       </c>
-      <c r="L11" s="17">
+      <c r="M11" s="17">
         <f>'크기'!F15</f>
         <v/>
       </c>
-      <c r="M11" s="17">
+      <c r="N11" s="17">
         <f>'크기'!F13</f>
         <v/>
       </c>
@@ -3706,23 +4107,24 @@
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr"/>
-      <c r="I12" s="17">
+      <c r="I12" s="7" t="inlineStr"/>
+      <c r="J12" s="17">
         <f>'크기'!H17</f>
         <v/>
       </c>
-      <c r="J12" s="17">
+      <c r="K12" s="17">
         <f>'크기'!H16</f>
         <v/>
       </c>
-      <c r="K12" s="17">
+      <c r="L12" s="17">
         <f>'크기'!H14</f>
         <v/>
       </c>
-      <c r="L12" s="17">
+      <c r="M12" s="17">
         <f>'크기'!H15</f>
         <v/>
       </c>
-      <c r="M12" s="17">
+      <c r="N12" s="17">
         <f>'크기'!H13</f>
         <v/>
       </c>
@@ -3766,23 +4168,24 @@
           <t>화 +20%</t>
         </is>
       </c>
-      <c r="I13" s="17">
+      <c r="I13" s="7" t="inlineStr"/>
+      <c r="J13" s="17">
         <f>'크기'!I17</f>
         <v/>
       </c>
-      <c r="J13" s="17">
+      <c r="K13" s="17">
         <f>'크기'!I16</f>
         <v/>
       </c>
-      <c r="K13" s="17">
+      <c r="L13" s="17">
         <f>'크기'!I14</f>
         <v/>
       </c>
-      <c r="L13" s="17">
+      <c r="M13" s="17">
         <f>'크기'!I15</f>
         <v/>
       </c>
-      <c r="M13" s="17">
+      <c r="N13" s="17">
         <f>'크기'!I13</f>
         <v/>
       </c>
@@ -3823,24 +4226,29 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr"/>
-      <c r="I14" s="17">
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>토 +25%</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr"/>
+      <c r="J14" s="17">
         <f>'크기'!I17</f>
         <v/>
       </c>
-      <c r="J14" s="17">
+      <c r="K14" s="17">
         <f>'크기'!I16</f>
         <v/>
       </c>
-      <c r="K14" s="17">
+      <c r="L14" s="17">
         <f>'크기'!I14</f>
         <v/>
       </c>
-      <c r="L14" s="17">
+      <c r="M14" s="17">
         <f>'크기'!I15</f>
         <v/>
       </c>
-      <c r="M14" s="17">
+      <c r="N14" s="17">
         <f>'크기'!I13</f>
         <v/>
       </c>
@@ -3871,33 +4279,34 @@
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>중형</t>
+          <t>소형</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>큼</t>
         </is>
       </c>
       <c r="H15" s="7" t="inlineStr"/>
-      <c r="I15" s="17">
-        <f>'크기'!F17</f>
-        <v/>
-      </c>
+      <c r="I15" s="7" t="inlineStr"/>
       <c r="J15" s="17">
-        <f>'크기'!F16</f>
+        <f>'크기'!D17</f>
         <v/>
       </c>
       <c r="K15" s="17">
-        <f>'크기'!F14</f>
+        <f>'크기'!D16</f>
         <v/>
       </c>
       <c r="L15" s="17">
-        <f>'크기'!F15</f>
+        <f>'크기'!D14</f>
         <v/>
       </c>
       <c r="M15" s="17">
-        <f>'크기'!F13</f>
+        <f>'크기'!D15</f>
+        <v/>
+      </c>
+      <c r="N15" s="17">
+        <f>'크기'!D13</f>
         <v/>
       </c>
     </row>
@@ -3936,23 +4345,24 @@
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr"/>
-      <c r="I16" s="17">
+      <c r="I16" s="7" t="inlineStr"/>
+      <c r="J16" s="17">
         <f>'크기'!C17</f>
         <v/>
       </c>
-      <c r="J16" s="17">
+      <c r="K16" s="17">
         <f>'크기'!C16</f>
         <v/>
       </c>
-      <c r="K16" s="17">
+      <c r="L16" s="17">
         <f>'크기'!C14</f>
         <v/>
       </c>
-      <c r="L16" s="17">
+      <c r="M16" s="17">
         <f>'크기'!C15</f>
         <v/>
       </c>
-      <c r="M16" s="17">
+      <c r="N16" s="17">
         <f>'크기'!C13</f>
         <v/>
       </c>
@@ -3983,7 +4393,7 @@
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>중형</t>
+          <t>소형</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
@@ -3992,24 +4402,25 @@
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr"/>
-      <c r="I17" s="17">
-        <f>'크기'!G17</f>
-        <v/>
-      </c>
+      <c r="I17" s="7" t="inlineStr"/>
       <c r="J17" s="17">
-        <f>'크기'!G16</f>
+        <f>'크기'!D17</f>
         <v/>
       </c>
       <c r="K17" s="17">
-        <f>'크기'!G14</f>
+        <f>'크기'!D16</f>
         <v/>
       </c>
       <c r="L17" s="17">
-        <f>'크기'!G15</f>
+        <f>'크기'!D14</f>
         <v/>
       </c>
       <c r="M17" s="17">
-        <f>'크기'!G13</f>
+        <f>'크기'!D15</f>
+        <v/>
+      </c>
+      <c r="N17" s="17">
+        <f>'크기'!D13</f>
         <v/>
       </c>
     </row>
@@ -4048,23 +4459,28 @@
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr"/>
-      <c r="I18" s="17">
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>사</t>
+        </is>
+      </c>
+      <c r="J18" s="17">
         <f>'크기'!F17</f>
         <v/>
       </c>
-      <c r="J18" s="17">
+      <c r="K18" s="17">
         <f>'크기'!F16</f>
         <v/>
       </c>
-      <c r="K18" s="17">
+      <c r="L18" s="17">
         <f>'크기'!F14</f>
         <v/>
       </c>
-      <c r="L18" s="17">
+      <c r="M18" s="17">
         <f>'크기'!F15</f>
         <v/>
       </c>
-      <c r="M18" s="17">
+      <c r="N18" s="17">
         <f>'크기'!F13</f>
         <v/>
       </c>
@@ -4104,23 +4520,28 @@
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr"/>
-      <c r="I19" s="17">
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>사</t>
+        </is>
+      </c>
+      <c r="J19" s="17">
         <f>'크기'!G17</f>
         <v/>
       </c>
-      <c r="J19" s="17">
+      <c r="K19" s="17">
         <f>'크기'!G16</f>
         <v/>
       </c>
-      <c r="K19" s="17">
+      <c r="L19" s="17">
         <f>'크기'!G14</f>
         <v/>
       </c>
-      <c r="L19" s="17">
+      <c r="M19" s="17">
         <f>'크기'!G15</f>
         <v/>
       </c>
-      <c r="M19" s="17">
+      <c r="N19" s="17">
         <f>'크기'!G13</f>
         <v/>
       </c>
@@ -4160,23 +4581,28 @@
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr"/>
-      <c r="I20" s="17">
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>사</t>
+        </is>
+      </c>
+      <c r="J20" s="17">
         <f>'크기'!H17</f>
         <v/>
       </c>
-      <c r="J20" s="17">
+      <c r="K20" s="17">
         <f>'크기'!H16</f>
         <v/>
       </c>
-      <c r="K20" s="17">
+      <c r="L20" s="17">
         <f>'크기'!H14</f>
         <v/>
       </c>
-      <c r="L20" s="17">
+      <c r="M20" s="17">
         <f>'크기'!H15</f>
         <v/>
       </c>
-      <c r="M20" s="17">
+      <c r="N20" s="17">
         <f>'크기'!H13</f>
         <v/>
       </c>
@@ -4216,23 +4642,28 @@
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr"/>
-      <c r="I21" s="17">
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>사</t>
+        </is>
+      </c>
+      <c r="J21" s="17">
         <f>'크기'!G17</f>
         <v/>
       </c>
-      <c r="J21" s="17">
+      <c r="K21" s="17">
         <f>'크기'!G16</f>
         <v/>
       </c>
-      <c r="K21" s="17">
+      <c r="L21" s="17">
         <f>'크기'!G14</f>
         <v/>
       </c>
-      <c r="L21" s="17">
+      <c r="M21" s="17">
         <f>'크기'!G15</f>
         <v/>
       </c>
-      <c r="M21" s="17">
+      <c r="N21" s="17">
         <f>'크기'!G13</f>
         <v/>
       </c>
@@ -4272,23 +4703,28 @@
         </is>
       </c>
       <c r="H22" s="7" t="inlineStr"/>
-      <c r="I22" s="17">
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>사</t>
+        </is>
+      </c>
+      <c r="J22" s="17">
         <f>'크기'!G17</f>
         <v/>
       </c>
-      <c r="J22" s="17">
+      <c r="K22" s="17">
         <f>'크기'!G16</f>
         <v/>
       </c>
-      <c r="K22" s="17">
+      <c r="L22" s="17">
         <f>'크기'!G14</f>
         <v/>
       </c>
-      <c r="L22" s="17">
+      <c r="M22" s="17">
         <f>'크기'!G15</f>
         <v/>
       </c>
-      <c r="M22" s="17">
+      <c r="N22" s="17">
         <f>'크기'!G13</f>
         <v/>
       </c>
@@ -4329,26 +4765,27 @@
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>수 +40%</t>
-        </is>
-      </c>
-      <c r="I23" s="17">
+          <t>목 +40%</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr"/>
+      <c r="J23" s="17">
         <f>'크기'!J17</f>
         <v/>
       </c>
-      <c r="J23" s="17">
+      <c r="K23" s="17">
         <f>'크기'!J16</f>
         <v/>
       </c>
-      <c r="K23" s="17">
+      <c r="L23" s="17">
         <f>'크기'!J14</f>
         <v/>
       </c>
-      <c r="L23" s="17">
+      <c r="M23" s="17">
         <f>'크기'!J15</f>
         <v/>
       </c>
-      <c r="M23" s="17">
+      <c r="N23" s="17">
         <f>'크기'!J13</f>
         <v/>
       </c>
@@ -4389,24 +4826,33 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="H24" s="7" t="inlineStr"/>
-      <c r="I24" s="17">
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>목 +25%</t>
+        </is>
+      </c>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>사</t>
+        </is>
+      </c>
+      <c r="J24" s="17">
         <f>'크기'!I17</f>
         <v/>
       </c>
-      <c r="J24" s="17">
+      <c r="K24" s="17">
         <f>'크기'!I16</f>
         <v/>
       </c>
-      <c r="K24" s="17">
+      <c r="L24" s="17">
         <f>'크기'!I14</f>
         <v/>
       </c>
-      <c r="L24" s="17">
+      <c r="M24" s="17">
         <f>'크기'!I15</f>
         <v/>
       </c>
-      <c r="M24" s="17">
+      <c r="N24" s="17">
         <f>'크기'!I13</f>
         <v/>
       </c>
@@ -4446,23 +4892,24 @@
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr"/>
-      <c r="I25" s="17">
+      <c r="I25" s="7" t="inlineStr"/>
+      <c r="J25" s="17">
         <f>'크기'!B17</f>
         <v/>
       </c>
-      <c r="J25" s="17">
+      <c r="K25" s="17">
         <f>'크기'!B16</f>
         <v/>
       </c>
-      <c r="K25" s="17">
+      <c r="L25" s="17">
         <f>'크기'!B14</f>
         <v/>
       </c>
-      <c r="L25" s="17">
+      <c r="M25" s="17">
         <f>'크기'!B15</f>
         <v/>
       </c>
-      <c r="M25" s="17">
+      <c r="N25" s="17">
         <f>'크기'!B13</f>
         <v/>
       </c>
@@ -4502,23 +4949,28 @@
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr"/>
-      <c r="I26" s="17">
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>정</t>
+        </is>
+      </c>
+      <c r="J26" s="17">
         <f>'크기'!F17</f>
         <v/>
       </c>
-      <c r="J26" s="17">
+      <c r="K26" s="17">
         <f>'크기'!F16</f>
         <v/>
       </c>
-      <c r="K26" s="17">
+      <c r="L26" s="17">
         <f>'크기'!F14</f>
         <v/>
       </c>
-      <c r="L26" s="17">
+      <c r="M26" s="17">
         <f>'크기'!F15</f>
         <v/>
       </c>
-      <c r="M26" s="17">
+      <c r="N26" s="17">
         <f>'크기'!F13</f>
         <v/>
       </c>
@@ -4558,23 +5010,28 @@
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr"/>
-      <c r="I27" s="17">
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>정</t>
+        </is>
+      </c>
+      <c r="J27" s="17">
         <f>'크기'!F17</f>
         <v/>
       </c>
-      <c r="J27" s="17">
+      <c r="K27" s="17">
         <f>'크기'!F16</f>
         <v/>
       </c>
-      <c r="K27" s="17">
+      <c r="L27" s="17">
         <f>'크기'!F14</f>
         <v/>
       </c>
-      <c r="L27" s="17">
+      <c r="M27" s="17">
         <f>'크기'!F15</f>
         <v/>
       </c>
-      <c r="M27" s="17">
+      <c r="N27" s="17">
         <f>'크기'!F13</f>
         <v/>
       </c>
@@ -4614,23 +5071,28 @@
         </is>
       </c>
       <c r="H28" s="7" t="inlineStr"/>
-      <c r="I28" s="17">
+      <c r="I28" s="7" t="inlineStr">
+        <is>
+          <t>정</t>
+        </is>
+      </c>
+      <c r="J28" s="17">
         <f>'크기'!F17</f>
         <v/>
       </c>
-      <c r="J28" s="17">
+      <c r="K28" s="17">
         <f>'크기'!F16</f>
         <v/>
       </c>
-      <c r="K28" s="17">
+      <c r="L28" s="17">
         <f>'크기'!F14</f>
         <v/>
       </c>
-      <c r="L28" s="17">
+      <c r="M28" s="17">
         <f>'크기'!F15</f>
         <v/>
       </c>
-      <c r="M28" s="17">
+      <c r="N28" s="17">
         <f>'크기'!F13</f>
         <v/>
       </c>
@@ -4670,23 +5132,28 @@
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr"/>
-      <c r="I29" s="17">
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>정</t>
+        </is>
+      </c>
+      <c r="J29" s="17">
         <f>'크기'!E17</f>
         <v/>
       </c>
-      <c r="J29" s="17">
+      <c r="K29" s="17">
         <f>'크기'!E16</f>
         <v/>
       </c>
-      <c r="K29" s="17">
+      <c r="L29" s="17">
         <f>'크기'!E14</f>
         <v/>
       </c>
-      <c r="L29" s="17">
+      <c r="M29" s="17">
         <f>'크기'!E15</f>
         <v/>
       </c>
-      <c r="M29" s="17">
+      <c r="N29" s="17">
         <f>'크기'!E13</f>
         <v/>
       </c>
@@ -4726,23 +5193,24 @@
         </is>
       </c>
       <c r="H30" s="7" t="inlineStr"/>
-      <c r="I30" s="17">
+      <c r="I30" s="7" t="inlineStr"/>
+      <c r="J30" s="17">
         <f>'크기'!I17</f>
         <v/>
       </c>
-      <c r="J30" s="17">
+      <c r="K30" s="17">
         <f>'크기'!I16</f>
         <v/>
       </c>
-      <c r="K30" s="17">
+      <c r="L30" s="17">
         <f>'크기'!I14</f>
         <v/>
       </c>
-      <c r="L30" s="17">
+      <c r="M30" s="17">
         <f>'크기'!I15</f>
         <v/>
       </c>
-      <c r="M30" s="17">
+      <c r="N30" s="17">
         <f>'크기'!I13</f>
         <v/>
       </c>
@@ -4773,7 +5241,7 @@
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>중형</t>
+          <t>소형</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
@@ -4782,24 +5250,25 @@
         </is>
       </c>
       <c r="H31" s="7" t="inlineStr"/>
-      <c r="I31" s="17">
-        <f>'크기'!G17</f>
-        <v/>
-      </c>
+      <c r="I31" s="7" t="inlineStr"/>
       <c r="J31" s="17">
-        <f>'크기'!G16</f>
+        <f>'크기'!D17</f>
         <v/>
       </c>
       <c r="K31" s="17">
-        <f>'크기'!G14</f>
+        <f>'크기'!D16</f>
         <v/>
       </c>
       <c r="L31" s="17">
-        <f>'크기'!G15</f>
+        <f>'크기'!D14</f>
         <v/>
       </c>
       <c r="M31" s="17">
-        <f>'크기'!G13</f>
+        <f>'크기'!D15</f>
+        <v/>
+      </c>
+      <c r="N31" s="17">
+        <f>'크기'!D13</f>
         <v/>
       </c>
     </row>
@@ -4829,37 +5298,38 @@
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>중형</t>
+          <t>소형</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>작음</t>
+          <t>큼</t>
         </is>
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>토 +20%</t>
-        </is>
-      </c>
-      <c r="I32" s="17">
-        <f>'크기'!E17</f>
-        <v/>
-      </c>
+          <t>화 +40%</t>
+        </is>
+      </c>
+      <c r="I32" s="7" t="inlineStr"/>
       <c r="J32" s="17">
-        <f>'크기'!E16</f>
+        <f>'크기'!D17</f>
         <v/>
       </c>
       <c r="K32" s="17">
-        <f>'크기'!E14</f>
+        <f>'크기'!D16</f>
         <v/>
       </c>
       <c r="L32" s="17">
-        <f>'크기'!E15</f>
+        <f>'크기'!D14</f>
         <v/>
       </c>
       <c r="M32" s="17">
-        <f>'크기'!E13</f>
+        <f>'크기'!D15</f>
+        <v/>
+      </c>
+      <c r="N32" s="17">
+        <f>'크기'!D13</f>
         <v/>
       </c>
     </row>
@@ -4898,23 +5368,28 @@
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr"/>
-      <c r="I33" s="17">
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t>정</t>
+        </is>
+      </c>
+      <c r="J33" s="17">
         <f>'크기'!H17</f>
         <v/>
       </c>
-      <c r="J33" s="17">
+      <c r="K33" s="17">
         <f>'크기'!H16</f>
         <v/>
       </c>
-      <c r="K33" s="17">
+      <c r="L33" s="17">
         <f>'크기'!H14</f>
         <v/>
       </c>
-      <c r="L33" s="17">
+      <c r="M33" s="17">
         <f>'크기'!H15</f>
         <v/>
       </c>
-      <c r="M33" s="17">
+      <c r="N33" s="17">
         <f>'크기'!H13</f>
         <v/>
       </c>
@@ -4955,24 +5430,33 @@
           <t>큼</t>
         </is>
       </c>
-      <c r="H34" s="7" t="inlineStr"/>
-      <c r="I34" s="17">
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>금 +25%</t>
+        </is>
+      </c>
+      <c r="I34" s="7" t="inlineStr">
+        <is>
+          <t>정</t>
+        </is>
+      </c>
+      <c r="J34" s="17">
         <f>'크기'!J17</f>
         <v/>
       </c>
-      <c r="J34" s="17">
+      <c r="K34" s="17">
         <f>'크기'!J16</f>
         <v/>
       </c>
-      <c r="K34" s="17">
+      <c r="L34" s="17">
         <f>'크기'!J14</f>
         <v/>
       </c>
-      <c r="L34" s="17">
+      <c r="M34" s="17">
         <f>'크기'!J15</f>
         <v/>
       </c>
-      <c r="M34" s="17">
+      <c r="N34" s="17">
         <f>'크기'!J13</f>
         <v/>
       </c>
@@ -5010,29 +5494,34 @@
         </is>
       </c>
       <c r="H35" s="7" t="inlineStr"/>
-      <c r="I35" s="17">
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>마</t>
+        </is>
+      </c>
+      <c r="J35" s="17">
         <f>'크기'!F17</f>
         <v/>
       </c>
-      <c r="J35" s="17">
+      <c r="K35" s="17">
         <f>'크기'!F16</f>
         <v/>
       </c>
-      <c r="K35" s="17">
+      <c r="L35" s="17">
         <f>'크기'!F14</f>
         <v/>
       </c>
-      <c r="L35" s="17">
+      <c r="M35" s="17">
         <f>'크기'!F15</f>
         <v/>
       </c>
-      <c r="M35" s="17">
+      <c r="N35" s="17">
         <f>'크기'!F13</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="I5:M35">
+  <conditionalFormatting sqref="J5:N35">
     <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
       <formula>0.0001</formula>
     </cfRule>
@@ -5050,26 +5539,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>모든 상성이 겹쳤을 때 (오행 × 병기 × 크기, 지력 · 약점 · 경지 · 정마사 빼고)</t>
+          <t>모든 상성이 겹쳤을 때 — 상한 전 · 상한 후</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>조정 전 값은 「계수」 C열, 지금 값은 D열로 계산</t>
+          <t>오행 × (병기 × 크기, ±30%) × 정마사 × 약점. 경지 압제는 따로. 두목은 오행 · 병기 · 크기 · 정마사가 절반</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5570,12 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>조정 전</t>
+          <t>상한 전</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>지금</t>
+          <t>상한 후 (게임)</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -5098,31 +5587,35 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>주는 피해 최고 (창이 대형)</t>
+          <t>일반 요수 · 주는 피해 최고 (오행 · 병기 · 창→대형 · 정마사)</t>
         </is>
       </c>
       <c r="B5" s="18">
-        <f>(1+'계수'!C5)*(1+'계수'!C7)*(1+'계수'!C12)</f>
-        <v/>
-      </c>
-      <c r="C5" s="18">
-        <f>(1+'계수'!D5)*(1+'계수'!D7)*(1+'계수'!D12)</f>
-        <v/>
-      </c>
-      <c r="D5" s="5" t="inlineStr"/>
+        <f>(1+'계수'!$D$5)*MIN(1+'계수'!$D$27,(1+'계수'!$D$7)*(1+'계수'!$D$12))*(1+'계수'!$D$18)</f>
+        <v/>
+      </c>
+      <c r="C5" s="19">
+        <f>MAX('계수'!$D$28,MIN('계수'!$D$29,B5))</f>
+        <v/>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>병기 × 크기는 ±30%에서 먼저 잘림</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>주는 피해 최고 (크기 유리 보통)</t>
+          <t>일반 요수 · 주는 피해 최저</t>
         </is>
       </c>
       <c r="B6" s="18">
-        <f>(1+'계수'!C5)*(1+'계수'!C7)*(1+'계수'!C10)</f>
-        <v/>
-      </c>
-      <c r="C6" s="18">
-        <f>(1+'계수'!D5)*(1+'계수'!D7)*(1+'계수'!D10)</f>
+        <f>(1-'계수'!$D$5)*MAX(1-'계수'!$D$27,(1-'계수'!$D$8)*(1-'계수'!$D$11))*(1-'계수'!$D$18)</f>
+        <v/>
+      </c>
+      <c r="C6" s="19">
+        <f>MAX('계수'!$D$28,MIN('계수'!$D$29,B6))</f>
         <v/>
       </c>
       <c r="D6" s="5" t="inlineStr"/>
@@ -5130,15 +5623,15 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>주는 피해 최저</t>
+          <t>일반 요수 · 받는 피해 최악</t>
         </is>
       </c>
       <c r="B7" s="18">
-        <f>(1-'계수'!C5)*(1-'계수'!C8)*(1-'계수'!C11)</f>
-        <v/>
-      </c>
-      <c r="C7" s="18">
-        <f>(1-'계수'!D5)*(1-'계수'!D8)*(1-'계수'!D11)</f>
+        <f>(1+'계수'!$D$5)*(1+'계수'!$D$6)*(1+'계수'!$D$7)*(1+'계수'!$D$18)</f>
+        <v/>
+      </c>
+      <c r="C7" s="19">
+        <f>MAX('계수'!$D$30,MIN('계수'!$D$31,B7))</f>
         <v/>
       </c>
       <c r="D7" s="5" t="inlineStr"/>
@@ -5146,55 +5639,51 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>주는 피해 최저 (검)</t>
+          <t>일반 요수 · 받는 피해 최선</t>
         </is>
       </c>
       <c r="B8" s="18">
-        <f>(1-'계수'!C5)*(1-'계수'!C8)*(1-'계수'!C13)</f>
-        <v/>
-      </c>
-      <c r="C8" s="18">
-        <f>(1-'계수'!D5)*(1-'계수'!D8)*(1-'계수'!D13)</f>
-        <v/>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>검은 크기 불리가 덜 깎임</t>
-        </is>
-      </c>
+        <f>(1-'계수'!$D$5)*(1-'계수'!$D$8)*(1-'계수'!$D$18)</f>
+        <v/>
+      </c>
+      <c r="C8" s="19">
+        <f>MAX('계수'!$D$30,MIN('계수'!$D$31,B8))</f>
+        <v/>
+      </c>
+      <c r="D8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>받는 피해 최악</t>
+          <t>두목 · 주는 피해 최고</t>
         </is>
       </c>
       <c r="B9" s="18">
-        <f>(1+'계수'!C5)*(1+'계수'!C6)*(1+'계수'!C7)</f>
-        <v/>
-      </c>
-      <c r="C9" s="18">
-        <f>(1+'계수'!D5)*(1+'계수'!D6)*(1+'계수'!D7)</f>
+        <f>(1+'계수'!$D$5*'계수'!$D$23)*(1+(MIN(1+'계수'!$D$27,(1+'계수'!$D$7)*(1+'계수'!$D$12))-1)*'계수'!$D$23)*(1+'계수'!$D$18*'계수'!$D$23)</f>
+        <v/>
+      </c>
+      <c r="C9" s="19">
+        <f>MAX('계수'!$D$28,MIN('계수'!$D$29,B9))</f>
         <v/>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>크기는 받는 피해에 안 들어감</t>
+          <t>상성 절반</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>받는 피해 최선</t>
+          <t>두목 · 주는 피해 최저</t>
         </is>
       </c>
       <c r="B10" s="18">
-        <f>(1-'계수'!C5)*(1-'계수'!C8)</f>
-        <v/>
-      </c>
-      <c r="C10" s="18">
-        <f>(1-'계수'!D5)*(1-'계수'!D8)</f>
+        <f>(1-'계수'!$D$5*'계수'!$D$23)*(1+(MAX(1-'계수'!$D$27,(1-'계수'!$D$8)*(1-'계수'!$D$11))-1)*'계수'!$D$23)*(1-'계수'!$D$18*'계수'!$D$23)</f>
+        <v/>
+      </c>
+      <c r="C10" s="19">
+        <f>MAX('계수'!$D$28,MIN('계수'!$D$29,B10))</f>
         <v/>
       </c>
       <c r="D10" s="5" t="inlineStr"/>
@@ -5202,80 +5691,124 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>약점까지 겹친 최고 (염화석괴 · 창 · 수 기공)</t>
+          <t>두목 · 받는 피해 최악</t>
         </is>
       </c>
       <c r="B11" s="18">
-        <f>(1+'계수'!C5)*(1+'계수'!C7)*(1+'계수'!C12)*(1+'계수'!C16)</f>
-        <v/>
-      </c>
-      <c r="C11" s="18">
-        <f>(1+'계수'!D5)*(1+'계수'!D7)*(1+'계수'!D12)*(1+'계수'!D16)</f>
-        <v/>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>특수한 경우</t>
-        </is>
-      </c>
+        <f>(1+((1+'계수'!$D$5)*(1+'계수'!$D$6)-1)*'계수'!$D$23)*(1+'계수'!$D$7*'계수'!$D$23)*(1+'계수'!$D$18*'계수'!$D$23)</f>
+        <v/>
+      </c>
+      <c r="C11" s="19">
+        <f>MAX('계수'!$D$30,MIN('계수'!$D$31,B11))</f>
+        <v/>
+      </c>
+      <c r="D11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>두목 상대 주는 피해 최고 (창 · 이득 절반)</t>
+          <t>두목 · 받는 피해 최선</t>
         </is>
       </c>
       <c r="B12" s="18">
-        <f>(1+'계수'!C5*'계수'!C23)*(1+'계수'!C7*'계수'!C23)*(1+'계수'!C12*'계수'!C23)</f>
-        <v/>
-      </c>
-      <c r="C12" s="18">
-        <f>(1+'계수'!D5*'계수'!D23)*(1+'계수'!D7*'계수'!D23)*(1+'계수'!D12*'계수'!D23)</f>
-        <v/>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>두목은 모두 대형</t>
-        </is>
-      </c>
+        <f>(1-'계수'!$D$5*'계수'!$D$23)*(1-'계수'!$D$8*'계수'!$D$23)*(1-'계수'!$D$18*'계수'!$D$23)</f>
+        <v/>
+      </c>
+      <c r="C12" s="19">
+        <f>MAX('계수'!$D$30,MIN('계수'!$D$31,B12))</f>
+        <v/>
+      </c>
+      <c r="D12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>경지 3단계 위 + 주는 피해 최고</t>
+          <t>두목 · 고유 약점까지 (주는 최고 × 1.25)</t>
         </is>
       </c>
       <c r="B13" s="18">
-        <f>(1+'계수'!C5)*(1+'계수'!C7)*(1+'계수'!C12)*(1+'계수'!C19*'계수'!C20)</f>
-        <v/>
-      </c>
-      <c r="C13" s="18">
-        <f>(1+'계수'!D5)*(1+'계수'!D7)*(1+'계수'!D12)*(1+'계수'!D19*'계수'!D20)</f>
+        <f>(1+'계수'!$D$5*'계수'!$D$23)*(1+(MIN(1+'계수'!$D$27,(1+'계수'!$D$7)*(1+'계수'!$D$12))-1)*'계수'!$D$23)*(1+'계수'!$D$18*'계수'!$D$23)*(1+'계수'!$D$32)</f>
+        <v/>
+      </c>
+      <c r="C13" s="19">
+        <f>MAX('계수'!$D$28,MIN('계수'!$D$29,B13))</f>
         <v/>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>참고</t>
+          <t>약점은 줄지 않음 (오행은 약점 오행이라 상극 아님 → 실제는 이보다 낮음)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>주는 피해 폭 (최고 ÷ 최저)</t>
-        </is>
-      </c>
-      <c r="B14" s="19">
-        <f>B5/B7</f>
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>전부 겹친 최고 (오성 오행 위력 · 약점 40% · 정마사 포함)</t>
+        </is>
+      </c>
+      <c r="B14" s="18">
+        <f>(1+'계수'!$D$5+'계수'!$D$33)*MIN(1+'계수'!$D$27,(1+'계수'!$D$7)*(1+'계수'!$D$12))*(1+'계수'!$D$18)*(1+'계수'!$D$16)</f>
         <v/>
       </c>
       <c r="C14" s="19">
-        <f>C5/C7</f>
+        <f>MAX('계수'!$D$28,MIN('계수'!$D$29,B14))</f>
         <v/>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>작을수록 상성이 덜 극단적</t>
+          <t>상한 1.8배에서 잘림</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>일반 요수 · 주는 피해 폭 (최고 ÷ 최저)</t>
+        </is>
+      </c>
+      <c r="B15" s="19">
+        <f>B5/B6</f>
+        <v/>
+      </c>
+      <c r="C15" s="19">
+        <f>C5/C6</f>
+        <v/>
+      </c>
+      <c r="D15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>두목 · 주는 피해 폭 (최고 ÷ 최저)</t>
+        </is>
+      </c>
+      <c r="B16" s="19">
+        <f>B9/B10</f>
+        <v/>
+      </c>
+      <c r="C16" s="19">
+        <f>C9/C10</f>
+        <v/>
+      </c>
+      <c r="D16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>경지 3단계 위일 때 곱 (상한 밖)</t>
+        </is>
+      </c>
+      <c r="B17" s="18">
+        <f>1+'계수'!$D$19*'계수'!$D$20</f>
+        <v/>
+      </c>
+      <c r="C17" s="18">
+        <f>1+'계수'!$D$19*'계수'!$D$20</f>
+        <v/>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>상한 후 값에 다시 곱함</t>
         </is>
       </c>
     </row>

--- a/gangho/docs/상성시스템_총정리.xlsx
+++ b/gangho/docs/상성시스템_총정리.xlsx
@@ -719,7 +719,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>청령목괴 ← 화 · 염화석괴 ← 목 +40% · 빙화수요 ← 화 +40% · 두목 셋 ← 토 · 목 · 금 +25%</t>
+          <t>청령목괴 ← 화 +20% · 염화석괴 ← 목 +40% · 빙화수요 ← 화 +40% (두목은 고유 약점 없음)</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>오행 고리 밖의 조합. 두목에게도 줄지 않음</t>
+          <t>오행 고리 밖의 조합</t>
         </is>
       </c>
     </row>
@@ -783,7 +783,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>이득 · 손해 모두 절반 (주는 · 받는 피해 · 명중 모두)</t>
+          <t>이득 · 손해 모두 절반 (주는 · 받는 피해 · 명중 모두), 고유 약점 없음</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>격이 달라 상성이 절반만 통함. 고유 약점 · 경지 압제는 그대로</t>
+          <t>격이 달라 상성이 절반만 통함. 경지 압제는 그대로</t>
         </is>
       </c>
     </row>
@@ -1712,14 +1712,14 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>두목 고유 약점 (적염 호랑이 ← 토 · 적패천 ← 목 · 벽해룡 ← 금)</t>
+          <t>두목 고유 약점 (없앰 — 유저 결정)</t>
         </is>
       </c>
       <c r="C32" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="D32" s="12" t="n">
-        <v>0.25</v>
+      <c r="D32" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="E32" s="9">
         <f>D32-C32</f>
@@ -4226,11 +4226,7 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
-        <is>
-          <t>토 +25%</t>
-        </is>
-      </c>
+      <c r="H14" s="7" t="inlineStr"/>
       <c r="I14" s="7" t="inlineStr"/>
       <c r="J14" s="17">
         <f>'크기'!I17</f>
@@ -4826,11 +4822,7 @@
           <t>보통</t>
         </is>
       </c>
-      <c r="H24" s="7" t="inlineStr">
-        <is>
-          <t>목 +25%</t>
-        </is>
-      </c>
+      <c r="H24" s="7" t="inlineStr"/>
       <c r="I24" s="7" t="inlineStr">
         <is>
           <t>사</t>
@@ -5430,11 +5422,7 @@
           <t>큼</t>
         </is>
       </c>
-      <c r="H34" s="7" t="inlineStr">
-        <is>
-          <t>금 +25%</t>
-        </is>
-      </c>
+      <c r="H34" s="7" t="inlineStr"/>
       <c r="I34" s="7" t="inlineStr">
         <is>
           <t>정</t>
@@ -5539,7 +5527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -5723,11 +5711,11 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>두목 · 고유 약점까지 (주는 최고 × 1.25)</t>
+          <t>전부 겹친 최고 (오성 오행 위력 · 약점 40% · 정마사 포함)</t>
         </is>
       </c>
       <c r="B13" s="18">
-        <f>(1+'계수'!$D$5*'계수'!$D$23)*(1+(MIN(1+'계수'!$D$27,(1+'계수'!$D$7)*(1+'계수'!$D$12))-1)*'계수'!$D$23)*(1+'계수'!$D$18*'계수'!$D$23)*(1+'계수'!$D$32)</f>
+        <f>(1+'계수'!$D$5+'계수'!$D$33)*MIN(1+'계수'!$D$27,(1+'계수'!$D$7)*(1+'계수'!$D$12))*(1+'계수'!$D$18)*(1+'계수'!$D$16)</f>
         <v/>
       </c>
       <c r="C13" s="19">
@@ -5736,77 +5724,57 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>약점은 줄지 않음 (오행은 약점 오행이라 상극 아님 → 실제는 이보다 낮음)</t>
+          <t>상한 1.8배에서 잘림</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>전부 겹친 최고 (오성 오행 위력 · 약점 40% · 정마사 포함)</t>
-        </is>
-      </c>
-      <c r="B14" s="18">
-        <f>(1+'계수'!$D$5+'계수'!$D$33)*MIN(1+'계수'!$D$27,(1+'계수'!$D$7)*(1+'계수'!$D$12))*(1+'계수'!$D$18)*(1+'계수'!$D$16)</f>
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>일반 요수 · 주는 피해 폭 (최고 ÷ 최저)</t>
+        </is>
+      </c>
+      <c r="B14" s="19">
+        <f>B5/B6</f>
         <v/>
       </c>
       <c r="C14" s="19">
-        <f>MAX('계수'!$D$28,MIN('계수'!$D$29,B14))</f>
-        <v/>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>상한 1.8배에서 잘림</t>
-        </is>
-      </c>
+        <f>C5/C6</f>
+        <v/>
+      </c>
+      <c r="D14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>일반 요수 · 주는 피해 폭 (최고 ÷ 최저)</t>
+          <t>두목 · 주는 피해 폭 (최고 ÷ 최저)</t>
         </is>
       </c>
       <c r="B15" s="19">
-        <f>B5/B6</f>
+        <f>B9/B10</f>
         <v/>
       </c>
       <c r="C15" s="19">
-        <f>C5/C6</f>
+        <f>C9/C10</f>
         <v/>
       </c>
       <c r="D15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>두목 · 주는 피해 폭 (최고 ÷ 최저)</t>
-        </is>
-      </c>
-      <c r="B16" s="19">
-        <f>B9/B10</f>
-        <v/>
-      </c>
-      <c r="C16" s="19">
-        <f>C9/C10</f>
-        <v/>
-      </c>
-      <c r="D16" s="5" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>경지 3단계 위일 때 곱 (상한 밖)</t>
         </is>
       </c>
-      <c r="B17" s="18">
+      <c r="B16" s="18">
         <f>1+'계수'!$D$19*'계수'!$D$20</f>
         <v/>
       </c>
-      <c r="C17" s="18">
+      <c r="C16" s="18">
         <f>1+'계수'!$D$19*'계수'!$D$20</f>
         <v/>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>상한 후 값에 다시 곱함</t>
         </is>

--- a/gangho/docs/상성시스템_총정리.xlsx
+++ b/gangho/docs/상성시스템_총정리.xlsx
@@ -665,7 +665,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>네 계열이 한 바퀴: 권장 › 검/도 › 창 › 암기 › 권장 (보완 대책 10월 3일)</t>
+          <t>다섯 계열, 저마다 둘을 이기고 둘에게 짐: 권장 › 검 · 도 / 검 › 창 · 암기 / 도 › 검 · 창 / 창 › 권장 · 암기 / 암기 › 권장 · 도 (10월 3일 검 · 도 분리)</t>
         </is>
       </c>
     </row>
@@ -800,44 +800,44 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>상한</t>
+          <t>비무 (사람끼리)</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>상성을 다 곱한 값</t>
+          <t>제자 ↔ 제자</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>주는 · 받는 피해</t>
+          <t>크기 상성</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>주는 0.6~1.8배 · 받는 0.7~1.5배</t>
+          <t>크기 상성 없음 (사람은 모두 중형이라 창이 늘 손해 보던 것을 뺌)</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>martial_arts.js AFFINITY_CAP</t>
+          <t>martial_arts.js DUEL_RULES · combat_engine.js affinity(opt.duel)</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>경지 압제는 상한 밖에서 따로 곱함</t>
+          <t>오행 · 병기 계열 · 정마사 · 경지는 그대로</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>경지 압제</t>
+          <t>상한</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>내 품계 ↔ 요수 경지(탐험지 단계)</t>
+          <t>상성을 다 곱한 값</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -847,47 +847,79 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>한 단계 차이마다 ±8%, 최대 3단계(±24%)</t>
+          <t>주는 0.6~1.8배 · 받는 0.7~1.5배</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>martial_arts.js COMBAT_RULES.realm</t>
+          <t>martial_arts.js AFFINITY_CAP</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>상성이 아니라 실력 차이 — 두목에게도 그대로</t>
+          <t>경지 압제는 상한 밖에서 따로 곱함</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
+          <t>경지 압제</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>내 품계 ↔ 요수 경지(탐험지 단계)</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>주는 · 받는 피해</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>한 단계 차이마다 ±8%, 최대 3단계(±24%)</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>martial_arts.js COMBAT_RULES.realm</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>상성이 아니라 실력 차이 — 두목에게도 그대로</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
           <t>지형</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>장착 경공의 지형 ↔ 탐험지 지형</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>강호행 기력 소모</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>맞으면 −20% · 안 맞아도 벌점 없음 · 경공 없으면 0</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>martial_arts.js AFFINITY.terrainMatch · terrainMiss · areas.js terrain</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>전투 피해와는 무관</t>
         </is>
@@ -2153,7 +2185,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2161,6 +2193,7 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2173,7 +2206,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>검과 도는 같은 계열(검/도). 짐승도 이빨 · 발톱을 병기 계열로 가짐</t>
+          <t>검과 도는 다른 계열 (10월 3일 분리). 짐승도 이빨 · 발톱을 병기 계열로 가짐</t>
         </is>
       </c>
     </row>
@@ -2197,15 +2230,20 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>검/도</t>
+          <t>검</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>도</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
           <t>창</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>암기</t>
         </is>
@@ -2224,18 +2262,23 @@
         <f>'계수'!$D$7</f>
         <v/>
       </c>
-      <c r="D6" s="15" t="n">
-        <v>0</v>
+      <c r="D6" s="15">
+        <f>'계수'!$D$7</f>
+        <v/>
       </c>
       <c r="E6" s="15">
         <f>-'계수'!$D$8</f>
         <v/>
       </c>
+      <c r="F6" s="15">
+        <f>-'계수'!$D$8</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>검/도</t>
+          <t>검</t>
         </is>
       </c>
       <c r="B7" s="15">
@@ -2246,24 +2289,30 @@
         <v>0</v>
       </c>
       <c r="D7" s="15">
+        <f>-'계수'!$D$8</f>
+        <v/>
+      </c>
+      <c r="E7" s="15">
         <f>'계수'!$D$7</f>
         <v/>
       </c>
-      <c r="E7" s="15" t="n">
-        <v>0</v>
+      <c r="F7" s="15">
+        <f>'계수'!$D$7</f>
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>창</t>
-        </is>
-      </c>
-      <c r="B8" s="15" t="n">
-        <v>0</v>
+          <t>도</t>
+        </is>
+      </c>
+      <c r="B8" s="15">
+        <f>-'계수'!$D$8</f>
+        <v/>
       </c>
       <c r="C8" s="15">
-        <f>-'계수'!$D$8</f>
+        <f>'계수'!$D$7</f>
         <v/>
       </c>
       <c r="D8" s="15" t="n">
@@ -2273,19 +2322,24 @@
         <f>'계수'!$D$7</f>
         <v/>
       </c>
+      <c r="F8" s="15">
+        <f>-'계수'!$D$8</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>암기</t>
+          <t>창</t>
         </is>
       </c>
       <c r="B9" s="15">
         <f>'계수'!$D$7</f>
         <v/>
       </c>
-      <c r="C9" s="15" t="n">
-        <v>0</v>
+      <c r="C9" s="15">
+        <f>-'계수'!$D$8</f>
+        <v/>
       </c>
       <c r="D9" s="15">
         <f>-'계수'!$D$8</f>
@@ -2294,230 +2348,279 @@
       <c r="E9" s="15" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="F9" s="15">
+        <f>'계수'!$D$7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>암기</t>
+        </is>
+      </c>
+      <c r="B10" s="15">
+        <f>'계수'!$D$7</f>
+        <v/>
+      </c>
+      <c r="C10" s="15">
+        <f>-'계수'!$D$8</f>
+        <v/>
+      </c>
+      <c r="D10" s="15">
+        <f>'계수'!$D$7</f>
+        <v/>
+      </c>
+      <c r="E10" s="15">
+        <f>-'계수'!$D$8</f>
+        <v/>
+      </c>
+      <c r="F10" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>받는 피해</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>나 \ 요수</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>권장</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>검/도</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>검</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>도</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>창</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>암기</t>
         </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="14" t="inlineStr">
-        <is>
-          <t>권장</t>
-        </is>
-      </c>
-      <c r="B13" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="15">
-        <f>-'계수'!$D$8</f>
-        <v/>
-      </c>
-      <c r="D13" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="15">
-        <f>'계수'!$D$7</f>
-        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t>검/도</t>
-        </is>
-      </c>
-      <c r="B14" s="15">
-        <f>'계수'!$D$7</f>
-        <v/>
-      </c>
-      <c r="C14" s="15" t="n">
+          <t>권장</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="n">
         <v>0</v>
+      </c>
+      <c r="C14" s="15">
+        <f>-'계수'!$D$8</f>
+        <v/>
       </c>
       <c r="D14" s="15">
         <f>-'계수'!$D$8</f>
         <v/>
       </c>
-      <c r="E14" s="15" t="n">
-        <v>0</v>
+      <c r="E14" s="15">
+        <f>'계수'!$D$7</f>
+        <v/>
+      </c>
+      <c r="F14" s="15">
+        <f>'계수'!$D$7</f>
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>창</t>
-        </is>
-      </c>
-      <c r="B15" s="15" t="n">
+          <t>검</t>
+        </is>
+      </c>
+      <c r="B15" s="15">
+        <f>'계수'!$D$7</f>
+        <v/>
+      </c>
+      <c r="C15" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="C15" s="15">
+      <c r="D15" s="15">
         <f>'계수'!$D$7</f>
         <v/>
-      </c>
-      <c r="D15" s="15" t="n">
-        <v>0</v>
       </c>
       <c r="E15" s="15">
         <f>-'계수'!$D$8</f>
         <v/>
       </c>
+      <c r="F15" s="15">
+        <f>-'계수'!$D$8</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
+          <t>도</t>
+        </is>
+      </c>
+      <c r="B16" s="15">
+        <f>'계수'!$D$7</f>
+        <v/>
+      </c>
+      <c r="C16" s="15">
+        <f>-'계수'!$D$8</f>
+        <v/>
+      </c>
+      <c r="D16" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="15">
+        <f>-'계수'!$D$8</f>
+        <v/>
+      </c>
+      <c r="F16" s="15">
+        <f>'계수'!$D$7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>창</t>
+        </is>
+      </c>
+      <c r="B17" s="15">
+        <f>-'계수'!$D$8</f>
+        <v/>
+      </c>
+      <c r="C17" s="15">
+        <f>'계수'!$D$7</f>
+        <v/>
+      </c>
+      <c r="D17" s="15">
+        <f>'계수'!$D$7</f>
+        <v/>
+      </c>
+      <c r="E17" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="15">
+        <f>-'계수'!$D$8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
           <t>암기</t>
         </is>
       </c>
-      <c r="B16" s="15">
+      <c r="B18" s="15">
         <f>-'계수'!$D$8</f>
         <v/>
       </c>
-      <c r="C16" s="15" t="n">
+      <c r="C18" s="15">
+        <f>'계수'!$D$7</f>
+        <v/>
+      </c>
+      <c r="D18" s="15">
+        <f>-'계수'!$D$8</f>
+        <v/>
+      </c>
+      <c r="E18" s="15">
+        <f>'계수'!$D$7</f>
+        <v/>
+      </c>
+      <c r="F18" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="D16" s="15">
-        <f>'계수'!$D$7</f>
-        <v/>
-      </c>
-      <c r="E16" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>명중 보정 (%p, 나 기준)</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>나 \ 요수</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>권장</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>검/도</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>검</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>도</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>창</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>암기</t>
         </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="14" t="inlineStr">
-        <is>
-          <t>권장</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" s="16">
-        <f>'계수'!$D$9</f>
-        <v/>
-      </c>
-      <c r="D20" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="16">
-        <f>-'계수'!$D$9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="14" t="inlineStr">
-        <is>
-          <t>검/도</t>
-        </is>
-      </c>
-      <c r="B21" s="16">
-        <f>-'계수'!$D$9</f>
-        <v/>
-      </c>
-      <c r="C21" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" s="16">
-        <f>'계수'!$D$9</f>
-        <v/>
-      </c>
-      <c r="E21" s="16" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
         <is>
-          <t>창</t>
+          <t>권장</t>
         </is>
       </c>
       <c r="B22" s="16" t="n">
         <v>0</v>
       </c>
       <c r="C22" s="16">
+        <f>'계수'!$D$9</f>
+        <v/>
+      </c>
+      <c r="D22" s="16">
+        <f>'계수'!$D$9</f>
+        <v/>
+      </c>
+      <c r="E22" s="16">
         <f>-'계수'!$D$9</f>
         <v/>
       </c>
-      <c r="D22" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="16">
-        <f>'계수'!$D$9</f>
+      <c r="F22" s="16">
+        <f>-'계수'!$D$9</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
         <is>
-          <t>암기</t>
+          <t>검</t>
         </is>
       </c>
       <c r="B23" s="16">
-        <f>'계수'!$D$9</f>
+        <f>-'계수'!$D$9</f>
         <v/>
       </c>
       <c r="C23" s="16" t="n">
@@ -2527,19 +2630,102 @@
         <f>-'계수'!$D$9</f>
         <v/>
       </c>
-      <c r="E23" s="16" t="n">
+      <c r="E23" s="16">
+        <f>'계수'!$D$9</f>
+        <v/>
+      </c>
+      <c r="F23" s="16">
+        <f>'계수'!$D$9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>도</t>
+        </is>
+      </c>
+      <c r="B24" s="16">
+        <f>-'계수'!$D$9</f>
+        <v/>
+      </c>
+      <c r="C24" s="16">
+        <f>'계수'!$D$9</f>
+        <v/>
+      </c>
+      <c r="D24" s="16" t="n">
         <v>0</v>
       </c>
+      <c r="E24" s="16">
+        <f>'계수'!$D$9</f>
+        <v/>
+      </c>
+      <c r="F24" s="16">
+        <f>-'계수'!$D$9</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>한 바퀴: 권장 › 검/도 › 창 › 암기 › 권장 — 모든 계열이 하나를 이기고 하나에게 지며, 맞은편(권장-창 · 검/도-암기)과는 호각</t>
+      <c r="A25" s="14" t="inlineStr">
+        <is>
+          <t>창</t>
+        </is>
+      </c>
+      <c r="B25" s="16">
+        <f>'계수'!$D$9</f>
+        <v/>
+      </c>
+      <c r="C25" s="16">
+        <f>-'계수'!$D$9</f>
+        <v/>
+      </c>
+      <c r="D25" s="16">
+        <f>-'계수'!$D$9</f>
+        <v/>
+      </c>
+      <c r="E25" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="16">
+        <f>'계수'!$D$9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>암기</t>
+        </is>
+      </c>
+      <c r="B26" s="16">
+        <f>'계수'!$D$9</f>
+        <v/>
+      </c>
+      <c r="C26" s="16">
+        <f>-'계수'!$D$9</f>
+        <v/>
+      </c>
+      <c r="D26" s="16">
+        <f>'계수'!$D$9</f>
+        <v/>
+      </c>
+      <c r="E26" s="16">
+        <f>-'계수'!$D$9</f>
+        <v/>
+      </c>
+      <c r="F26" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>다섯 갈래 순환: 저마다 둘을 이기고 둘에게 진다 (같은 계열끼리는 호각). 권장 › 검 · 도 · 검 › 창 · 암기 · 도 › 검 · 창 · 창 › 권장 · 암기 · 암기 › 권장 · 도</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B6:E9">
+  <conditionalFormatting sqref="B6:F10">
     <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
       <formula>0.0001</formula>
     </cfRule>
@@ -2547,7 +2733,7 @@
       <formula>-0.0001</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B20:E23">
+  <conditionalFormatting sqref="B22:F26">
     <cfRule type="cellIs" priority="3" operator="greaterThan" dxfId="0">
       <formula>0.0001</formula>
     </cfRule>
@@ -2555,7 +2741,7 @@
       <formula>-0.0001</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B13:E16">
+  <conditionalFormatting sqref="B14:F18">
     <cfRule type="cellIs" priority="5" operator="greaterThan" dxfId="1">
       <formula>0.0001</formula>
     </cfRule>
@@ -3796,7 +3982,7 @@
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>검/도</t>
+          <t>도</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
@@ -4624,7 +4810,7 @@
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>검/도</t>
+          <t>도</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
@@ -4685,7 +4871,7 @@
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>검/도</t>
+          <t>도</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
@@ -4809,7 +4995,7 @@
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>검/도</t>
+          <t>도</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
@@ -4927,7 +5113,7 @@
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>검/도</t>
+          <t>도</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
@@ -5468,7 +5654,7 @@
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>검/도</t>
+          <t>검</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
